--- a/artfynd/A 35927-2023 artfynd.xlsx
+++ b/artfynd/A 35927-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35927-2023 artfynd.xlsx
+++ b/artfynd/A 35927-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1054,6 +1054,356 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118125277</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97756</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pettersborg, 3km SV om Rambo, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>715186</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7110212</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>foton, både rundat nedre blad och djupflikiga, starkt färgade blommor</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118122845</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97874</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Pettersborg, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>715040</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7110105</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118122840</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97874</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Pettersborg, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>715205</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7110201</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35927-2023 artfynd.xlsx
+++ b/artfynd/A 35927-2023 artfynd.xlsx
@@ -1406,7 +1406,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118354699</v>
+        <v>118354909</v>
       </c>
       <c r="B8" t="n">
         <v>97880</v>
@@ -1439,26 +1439,17 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pettersborg, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715160</v>
+        <v>715066</v>
       </c>
       <c r="R8" t="n">
-        <v>7110179</v>
+        <v>7110138</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1490,7 +1481,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1500,12 +1491,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Luktar fortfarande otroligt gott, även om nattviolens blommning går mot sitt slut</t>
+          <t>Ytterligare 4 plantor med svag doft, 1 mer än dom andra</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1532,7 +1523,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118354909</v>
+        <v>118354699</v>
       </c>
       <c r="B9" t="n">
         <v>97880</v>
@@ -1565,17 +1556,26 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pettersborg, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715066</v>
+        <v>715160</v>
       </c>
       <c r="R9" t="n">
-        <v>7110138</v>
+        <v>7110179</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ytterligare 4 plantor med svag doft, 1 mer än dom andra</t>
+          <t>Luktar fortfarande otroligt gott, även om nattviolens blommning går mot sitt slut</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 35927-2023 artfynd.xlsx
+++ b/artfynd/A 35927-2023 artfynd.xlsx
@@ -1406,10 +1406,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118354909</v>
+        <v>118354699</v>
       </c>
       <c r="B8" t="n">
-        <v>97880</v>
+        <v>97887</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1439,17 +1439,26 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pettersborg, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715066</v>
+        <v>715160</v>
       </c>
       <c r="R8" t="n">
-        <v>7110138</v>
+        <v>7110179</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1490,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,12 +1500,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ytterligare 4 plantor med svag doft, 1 mer än dom andra</t>
+          <t>Luktar fortfarande otroligt gott, även om nattviolens blommning går mot sitt slut</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,10 +1532,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118354699</v>
+        <v>118354909</v>
       </c>
       <c r="B9" t="n">
-        <v>97880</v>
+        <v>97887</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1556,26 +1565,17 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pettersborg, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715160</v>
+        <v>715066</v>
       </c>
       <c r="R9" t="n">
-        <v>7110179</v>
+        <v>7110138</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Luktar fortfarande otroligt gott, även om nattviolens blommning går mot sitt slut</t>
+          <t>Ytterligare 4 plantor med svag doft, 1 mer än dom andra</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 35927-2023 artfynd.xlsx
+++ b/artfynd/A 35927-2023 artfynd.xlsx
@@ -1406,7 +1406,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118354699</v>
+        <v>118354909</v>
       </c>
       <c r="B8" t="n">
         <v>97887</v>
@@ -1439,26 +1439,17 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pettersborg, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715160</v>
+        <v>715066</v>
       </c>
       <c r="R8" t="n">
-        <v>7110179</v>
+        <v>7110138</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1490,7 +1481,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1500,12 +1491,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Luktar fortfarande otroligt gott, även om nattviolens blommning går mot sitt slut</t>
+          <t>Ytterligare 4 plantor med svag doft, 1 mer än dom andra</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1532,7 +1523,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118354909</v>
+        <v>118354699</v>
       </c>
       <c r="B9" t="n">
         <v>97887</v>
@@ -1565,17 +1556,26 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pettersborg, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715066</v>
+        <v>715160</v>
       </c>
       <c r="R9" t="n">
-        <v>7110138</v>
+        <v>7110179</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ytterligare 4 plantor med svag doft, 1 mer än dom andra</t>
+          <t>Luktar fortfarande otroligt gott, även om nattviolens blommning går mot sitt slut</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 35927-2023 artfynd.xlsx
+++ b/artfynd/A 35927-2023 artfynd.xlsx
@@ -1290,12 +1290,7 @@
         <v>118122840</v>
       </c>
       <c r="B7" t="n">
-        <v>97882</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98375</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35927-2023 artfynd.xlsx
+++ b/artfynd/A 35927-2023 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>118122840</v>
       </c>
       <c r="B7" t="n">
-        <v>98375</v>
+        <v>98377</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35927-2023 artfynd.xlsx
+++ b/artfynd/A 35927-2023 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>118122840</v>
       </c>
       <c r="B7" t="n">
-        <v>98377</v>
+        <v>98379</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35927-2023 artfynd.xlsx
+++ b/artfynd/A 35927-2023 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>118122840</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>98381</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35927-2023 artfynd.xlsx
+++ b/artfynd/A 35927-2023 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>118122840</v>
       </c>
       <c r="B7" t="n">
-        <v>98381</v>
+        <v>98385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35927-2023 artfynd.xlsx
+++ b/artfynd/A 35927-2023 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>118122840</v>
       </c>
       <c r="B7" t="n">
-        <v>98385</v>
+        <v>98388</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35927-2023 artfynd.xlsx
+++ b/artfynd/A 35927-2023 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>118122840</v>
       </c>
       <c r="B7" t="n">
-        <v>98388</v>
+        <v>98397</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
